--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486961_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486961_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9243</v>
+        <v>3.3241</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7004</v>
+        <v>2.8708</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2239</v>
+        <v>0.4532</v>
       </c>
       <c r="G2" t="n">
         <v>1.2763</v>
@@ -610,13 +610,13 @@
         <v>1.2321</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1757</v>
+        <v>0.5755</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0504</v>
+        <v>0.1201</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2261</v>
+        <v>0.4554</v>
       </c>
       <c r="V2" t="n">
         <v>0.2402</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7845</v>
+        <v>2.4452</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6666</v>
+        <v>3.268</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8821</v>
+        <v>-0.8228</v>
       </c>
       <c r="G3" t="n">
         <v>2.4479</v>
@@ -688,13 +688,13 @@
         <v>1.2321</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6159</v>
+        <v>1.2766</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5995</v>
+        <v>1.201</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0163</v>
+        <v>0.0756</v>
       </c>
       <c r="V3" t="n">
         <v>-0.4579</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>A. MORENO TRUJILLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3642</v>
+        <v>0.8897</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5896</v>
+        <v>2.7434</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.2253</v>
+        <v>-1.8537</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.798</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1746</v>
+        <v>2.424</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6234</v>
+        <v>-2.9285</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5165</v>
+        <v>2.8361</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2141</v>
+        <v>4.2572</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3024</v>
+        <v>-1.4211</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.3145</v>
+        <v>-3.3406</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3887</v>
+        <v>-1.8332</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.9258</v>
+        <v>-1.5074</v>
       </c>
       <c r="P4" t="n">
-        <v>1.2321</v>
+        <v>0.616</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2321</v>
+        <v>1.6427</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9302</v>
+        <v>0.4291</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0731</v>
+        <v>0.3447</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1429</v>
+        <v>0.0844</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. SIMEUNOVIC</t>
+          <t>J. PUIDET</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3107</v>
+        <v>0.4638</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8376</v>
+        <v>2.4115</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.5269</v>
+        <v>-1.9477</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.1848</v>
+        <v>0.4134</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1119</v>
+        <v>-0.4154</v>
       </c>
       <c r="I5" t="n">
-        <v>-4.2968</v>
+        <v>0.8288</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0892</v>
+        <v>4.8138</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9973</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.9081</v>
+        <v>4.2619</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.274</v>
+        <v>-4.4004</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8854</v>
+        <v>-0.9673</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.3887</v>
+        <v>-3.4332</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>-0.616</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0534</v>
+        <v>2.4641</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5571</v>
+        <v>0.6664</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3829</v>
+        <v>0.6778</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1742</v>
+        <v>-0.0114</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9384</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MORENO TRUJILLO</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0566</v>
+        <v>0.1847</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9453</v>
+        <v>2.3804</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.0019</v>
+        <v>-2.1957</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5044999999999999</v>
+        <v>-1.798</v>
       </c>
       <c r="H6" t="n">
-        <v>2.424</v>
+        <v>-1.1746</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.9285</v>
+        <v>-0.6234</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8361</v>
+        <v>1.5165</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2572</v>
+        <v>0.2141</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4211</v>
+        <v>1.3024</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.3406</v>
+        <v>-3.3145</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.8332</v>
+        <v>-1.3887</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.5074</v>
+        <v>-1.9258</v>
       </c>
       <c r="P6" t="n">
-        <v>0.616</v>
+        <v>1.2321</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5172</v>
+        <v>0.7506</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4534</v>
+        <v>0.8639</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0638</v>
+        <v>-0.1132</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3491</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PUIDET</t>
+          <t>D. SIMEUNOVIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2049</v>
+        <v>-0.3195</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8614</v>
+        <v>2.2371</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0663</v>
+        <v>-2.5565</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4134</v>
+        <v>-2.1848</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4154</v>
+        <v>2.1119</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8288</v>
+        <v>-4.2968</v>
       </c>
       <c r="J7" t="n">
-        <v>4.8138</v>
+        <v>2.0892</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5518999999999999</v>
+        <v>3.9973</v>
       </c>
       <c r="L7" t="n">
-        <v>4.2619</v>
+        <v>-1.9081</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.4004</v>
+        <v>-4.274</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9673</v>
+        <v>-1.8854</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.4332</v>
+        <v>-2.3887</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.616</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4641</v>
+        <v>2.0534</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0023</v>
+        <v>0.927</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1277</v>
+        <v>0.7824</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.13</v>
+        <v>0.1445</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.9384</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SANTANO BARTOLOME</t>
+          <t>K. CURFMAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3287</v>
+        <v>-0.9461000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7858000000000001</v>
+        <v>2.781</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1145</v>
+        <v>-3.7271</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0373</v>
+        <v>1.0571</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0323</v>
+        <v>-0.3345</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.005</v>
+        <v>1.3917</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6463</v>
+        <v>5.079</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6069</v>
+        <v>0.8565</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0395</v>
+        <v>4.2225</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6837</v>
+        <v>-4.0219</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6392</v>
+        <v>-1.191</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0445</v>
+        <v>-2.8308</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8214</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8214</v>
+        <v>1.6427</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0659</v>
+        <v>-0.0649</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1395</v>
+        <v>0.1045</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0736</v>
+        <v>-0.1694</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1786</v>
+        <v>-1.5277</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="X8" t="n">
         <v>-1.1786</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. CURFMAN</t>
+          <t>J. SANTANO BARTOLOME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6379</v>
+        <v>-1.0149</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2967</v>
+        <v>1.0996</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.9346</v>
+        <v>-2.1145</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0571</v>
+        <v>-1.0373</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3345</v>
+        <v>-0.0323</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3917</v>
+        <v>-1.005</v>
       </c>
       <c r="J9" t="n">
-        <v>5.079</v>
+        <v>0.6463</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8565</v>
+        <v>0.6069</v>
       </c>
       <c r="L9" t="n">
-        <v>4.2225</v>
+        <v>0.0395</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.0219</v>
+        <v>-1.6837</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.191</v>
+        <v>-0.6392</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.8308</v>
+        <v>-1.0445</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4107</v>
+        <v>0.8214</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6427</v>
+        <v>0.8214</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7566000000000001</v>
+        <v>0.3797</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3798</v>
+        <v>0.4533</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3769</v>
+        <v>-0.0736</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5277</v>
+        <v>-1.1786</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>-1.1786</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2495</v>
+        <v>-2.4622</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3874</v>
+        <v>1.9376</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.637</v>
+        <v>-4.3998</v>
       </c>
       <c r="G10" t="n">
         <v>1.9205</v>
@@ -1234,13 +1234,13 @@
         <v>1.0267</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.671</v>
+        <v>0.1163</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3139</v>
+        <v>0.2362</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3571</v>
+        <v>-0.12</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4189</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.906100000000002</v>
+        <v>2.5648</v>
       </c>
       <c r="E11" t="n">
-        <v>21.0708</v>
+        <v>21.7294</v>
       </c>
       <c r="F11" t="n">
-        <v>-19.1647</v>
+        <v>-19.1646</v>
       </c>
       <c r="G11" t="n">
         <v>1.5906</v>
@@ -1312,19 +1312,19 @@
         <v>13.3473</v>
       </c>
       <c r="S11" t="n">
-        <v>4.397699999999999</v>
+        <v>5.056299999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>4.1252</v>
+        <v>4.783900000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2722999999999999</v>
+        <v>0.2723000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.055400000000001</v>
+        <v>-3.0554</v>
       </c>
       <c r="W11" t="n">
-        <v>2.8603</v>
+        <v>2.860300000000001</v>
       </c>
       <c r="X11" t="n">
         <v>-5.9156</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.0809</v>
+        <v>5.834</v>
       </c>
       <c r="E12" t="n">
-        <v>5.0881</v>
+        <v>5.8204</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0072</v>
+        <v>0.0137</v>
       </c>
       <c r="G12" t="n">
         <v>1.0088</v>
@@ -1390,13 +1390,13 @@
         <v>2.0534</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5788</v>
+        <v>0.1743</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.651</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0722</v>
+        <v>0.0931</v>
       </c>
       <c r="V12" t="n">
         <v>2.5975</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3181</v>
+        <v>5.2543</v>
       </c>
       <c r="E13" t="n">
-        <v>6.09</v>
+        <v>6.7176</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7719</v>
+        <v>-1.4633</v>
       </c>
       <c r="G13" t="n">
         <v>3.5506</v>
@@ -1468,13 +1468,13 @@
         <v>2.2588</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4912</v>
+        <v>-0.555</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7169</v>
+        <v>-0.0892</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7744</v>
+        <v>-0.4658</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0913</v>
+        <v>5.0362</v>
       </c>
       <c r="E14" t="n">
-        <v>6.6148</v>
+        <v>7.2424</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.5235</v>
+        <v>-2.2062</v>
       </c>
       <c r="G14" t="n">
         <v>4.9258</v>
@@ -1546,13 +1546,13 @@
         <v>1.2321</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0399</v>
+        <v>-0.0949</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.651</v>
+        <v>-0.0234</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3889</v>
+        <v>-0.0716</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ANDREATTA</t>
+          <t>J. FANER CATALA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7169</v>
+        <v>-0.7319</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5586</v>
+        <v>3.5423</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2755</v>
+        <v>-4.2742</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.9137</v>
+        <v>1.4595</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.7164</v>
+        <v>-0.2402</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1973</v>
+        <v>1.6997</v>
       </c>
       <c r="J16" t="n">
-        <v>1.558</v>
+        <v>5.0185</v>
       </c>
       <c r="K16" t="n">
-        <v>0.782</v>
+        <v>1.9271</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7759</v>
+        <v>3.0914</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.4717</v>
+        <v>-3.559</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.4985</v>
+        <v>-2.1673</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9732</v>
+        <v>-1.3917</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4107</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4374</v>
+        <v>0.8214</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3282</v>
+        <v>-0.9163</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1513</v>
+        <v>-0.4495</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4795</v>
+        <v>-0.4668</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4579</v>
+        <v>-1.0698</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.7207</v>
+        <v>-1.0698</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. BAH</t>
+          <t>M. ANDREATTA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9623</v>
+        <v>-0.9976</v>
       </c>
       <c r="E17" t="n">
-        <v>3.055</v>
+        <v>1.6632</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.0172</v>
+        <v>-2.6609</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.6018</v>
+        <v>-1.9137</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.6048</v>
+        <v>-1.7164</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.997</v>
+        <v>-0.1973</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0375</v>
+        <v>1.558</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.8268</v>
+        <v>0.782</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7893</v>
+        <v>0.7759</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.5643</v>
+        <v>-3.4717</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.778</v>
+        <v>-2.4985</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.7863</v>
+        <v>-0.9732</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4374</v>
+        <v>0.4107</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R17" t="n">
         <v>1.4374</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7217</v>
+        <v>0.0475</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4333</v>
+        <v>-0.0467</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7117</v>
+        <v>0.0941</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4805</v>
+        <v>0.4579</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6591</v>
+        <v>1.1786</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1786</v>
+        <v>-0.7207</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. FANER CATALA</t>
+          <t>D. BAH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2794</v>
+        <v>-1.6055</v>
       </c>
       <c r="E18" t="n">
-        <v>3.333</v>
+        <v>1.9043</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.6124</v>
+        <v>-3.5099</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4595</v>
+        <v>-3.6018</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2402</v>
+        <v>-2.6048</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6997</v>
+        <v>-0.997</v>
       </c>
       <c r="J18" t="n">
-        <v>5.0185</v>
+        <v>-0.0375</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9271</v>
+        <v>-0.8268</v>
       </c>
       <c r="L18" t="n">
-        <v>3.0914</v>
+        <v>0.7893</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.559</v>
+        <v>-3.5643</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.1673</v>
+        <v>-1.778</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3917</v>
+        <v>-1.7863</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2053</v>
+        <v>1.4374</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8214</v>
+        <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4637</v>
+        <v>0.0784</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6587</v>
+        <v>0.2827</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.805</v>
+        <v>-0.2043</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0698</v>
+        <v>0.4805</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.6591</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0698</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0093</v>
+        <v>-3.0814</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1499</v>
+        <v>-0.2099</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.1592</v>
+        <v>-2.8715</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9224</v>
@@ -1936,13 +1936,13 @@
         <v>1.8481</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1719</v>
+        <v>0.0997</v>
       </c>
       <c r="T19" t="n">
-        <v>2.0725</v>
+        <v>0.7127</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.613</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.1357</v>
+        <v>-4.5429</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.8397</v>
+        <v>-3.5259</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.296</v>
+        <v>-1.0171</v>
       </c>
       <c r="G20" t="n">
         <v>-1.8894</v>
@@ -2014,13 +2014,13 @@
         <v>1.4374</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1662</v>
+        <v>-0.5734</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7246</v>
+        <v>-0.4108</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4416</v>
+        <v>-0.1626</v>
       </c>
       <c r="V20" t="n">
         <v>0.5893</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.4981</v>
+        <v>-5.1843</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.8851</v>
+        <v>-3.9897</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.613</v>
+        <v>-1.1946</v>
       </c>
       <c r="G21" t="n">
         <v>-4.2079</v>
@@ -2092,13 +2092,13 @@
         <v>1.6427</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8794999999999999</v>
+        <v>-0.5657</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2249</v>
+        <v>-0.3295</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6546999999999999</v>
+        <v>-0.2362</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.906099999999998</v>
+        <v>0.1861999999999986</v>
       </c>
       <c r="E22" t="n">
-        <v>19.1646</v>
+        <v>19.1647</v>
       </c>
       <c r="F22" t="n">
-        <v>-21.0706</v>
+        <v>-18.9787</v>
       </c>
       <c r="G22" t="n">
         <v>-1.590500000000001</v>
@@ -2146,7 +2146,7 @@
         <v>26.8686</v>
       </c>
       <c r="K22" t="n">
-        <v>9.702699999999998</v>
+        <v>9.7027</v>
       </c>
       <c r="L22" t="n">
         <v>17.1658</v>
@@ -2170,13 +2170,13 @@
         <v>14.374</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.397500000000001</v>
+        <v>-2.3054</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2726000000000006</v>
+        <v>-0.2725</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.1253</v>
+        <v>-2.0331</v>
       </c>
       <c r="V22" t="n">
         <v>3.0554</v>
